--- a/data/trans_camb/P1429-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1429-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,54</t>
         </is>
       </c>
     </row>
@@ -682,42 +682,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,14</t>
+          <t>0,2; 1,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 4,79</t>
+          <t>-1,98; 4,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 4,74</t>
+          <t>-1,39; 4,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 2,88</t>
+          <t>-2,5; 2,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,58</t>
+          <t>-0,86; 2,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 2,61</t>
+          <t>-0,55; 2,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,96</t>
+          <t>-0,93; 1,7</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>40,31%</t>
         </is>
       </c>
     </row>
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,8; 373,0</t>
+          <t>-55,86; 313,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,73; 332,22</t>
+          <t>-39,43; 363,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,02; 213,13</t>
+          <t>-55,19; 197,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,34; 384,14</t>
+          <t>-43,9; 399,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,97; 394,56</t>
+          <t>-31,57; 402,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 329,71</t>
+          <t>-42,32; 267,1</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>-0,02</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,68</t>
+          <t>-3,74</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 1,98</t>
+          <t>-0,2; 1,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,3</t>
+          <t>-0,72; 0,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,35</t>
+          <t>-0,63; 0,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,97; -1,5</t>
+          <t>-7,14; -1,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,48; -1,03</t>
+          <t>-6,64; -0,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,36; -0,97</t>
+          <t>-6,55; -1,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,37; -0,33</t>
+          <t>-3,39; -0,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,31; -0,41</t>
+          <t>-3,33; -0,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,27; -0,64</t>
+          <t>-3,29; -0,59</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-16,46%</t>
+          <t>-11,12%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-52,73%</t>
+          <t>-53,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-52,55%</t>
+          <t>-52,52%</t>
         </is>
       </c>
     </row>
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-79,98; -21,18</t>
+          <t>-81,44; -23,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,55; -16,25</t>
+          <t>-73,57; -7,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,6; -18,11</t>
+          <t>-72,7; -24,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-75,25; -7,27</t>
+          <t>-73,82; -6,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,33; -13,16</t>
+          <t>-73,43; -8,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-70,66; -19,88</t>
+          <t>-71,94; -19,65</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>-0,03</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,43</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,64</t>
+          <t>-0,95; 0,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,0</t>
+          <t>-1,56; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,6</t>
+          <t>-0,94; 0,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 2,05</t>
+          <t>-3,89; 2,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 0,05</t>
+          <t>-4,86; 0,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 3,05</t>
+          <t>-1,93; 3,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 1,04</t>
+          <t>-1,94; 1,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,87; -0,04</t>
+          <t>-2,77; 0,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,78</t>
+          <t>-1,12; 1,77</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-5,02%</t>
+          <t>-8,21%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-70,78; 111,24</t>
+          <t>-71,95; 83,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-91,16; 23,63</t>
+          <t>-90,8; 26,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-38,79; 133,28</t>
+          <t>-37,49; 143,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-68,78; 82,0</t>
+          <t>-66,92; 90,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-91,72; 30,53</t>
+          <t>-90,28; 24,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-35,04; 129,15</t>
+          <t>-34,18; 135,66</t>
         </is>
       </c>
     </row>
@@ -1282,22 +1282,22 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>2,1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3,74</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>2,47</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,74</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,47</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,76</t>
+          <t>4,08</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,02</t>
+          <t>3,24</t>
         </is>
       </c>
     </row>
@@ -1330,42 +1330,42 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 6,47</t>
+          <t>0,83; 5,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 7,27</t>
+          <t>0,39; 7,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 6,16</t>
+          <t>-1,08; 5,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 5,99</t>
+          <t>1,38; 7,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 3,68</t>
+          <t>0,25; 3,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 3,38</t>
+          <t>-0,26; 3,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,05</t>
+          <t>1,48; 5,14</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>102,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>149,73%</t>
+          <t>160,25%</t>
         </is>
       </c>
     </row>
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,7; 254,21</t>
+          <t>-0,16; 262,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,65; 239,71</t>
+          <t>-24,37; 210,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 216,5</t>
+          <t>19,75; 285,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,68; 270,86</t>
+          <t>1,66; 294,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 238,17</t>
+          <t>-15,08; 252,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>43,79; 366,76</t>
+          <t>46,4; 360,58</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,42</t>
+          <t>3,17</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,09</t>
+          <t>1,86</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,0</t>
+          <t>-2,04; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,0</t>
+          <t>-2,52; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,5</t>
+          <t>-0,81; 1,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 4,88</t>
+          <t>-0,94; 5,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 1,49</t>
+          <t>-3,11; 1,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,78</t>
+          <t>0,3; 5,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 2,52</t>
+          <t>-0,75; 2,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,57</t>
+          <t>-1,62; 0,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,33</t>
+          <t>0,3; 3,14</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>110,91%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>217,32%</t>
+          <t>200,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>209,98%</t>
+          <t>187,65%</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-56,27; 862,99</t>
+          <t>-47,59; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,85; 1085,22</t>
+          <t>-11,22; 997,02</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-48,66; 695,96</t>
+          <t>-52,07; 701,54</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>8,92; 1057,06</t>
+          <t>-3,91; 1081,04</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,64</t>
+          <t>1,59</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>1,94</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,72</t>
+          <t>1,7</t>
         </is>
       </c>
     </row>
@@ -1762,42 +1762,42 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,5</t>
+          <t>0,67; 3,05</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 1,01</t>
+          <t>-4,96; 0,76</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 0,95</t>
+          <t>-5,38; 0,76</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 5,09</t>
+          <t>-1,67; 4,62</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 0,53</t>
+          <t>-2,65; 0,38</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,2</t>
+          <t>-2,22; 1,16</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 3,47</t>
+          <t>-0,0; 3,55</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>79,82%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-80,89; 61,84</t>
+          <t>-82,99; 42,98</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-82,03; 53,94</t>
+          <t>-83,49; 42,25</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-24,17; 214,26</t>
+          <t>-29,16; 181,28</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-85,65; 51,81</t>
+          <t>-87,65; 36,02</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-74,62; 96,88</t>
+          <t>-72,73; 101,91</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 286,73</t>
+          <t>-0,24; 301,98</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>2,16</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>1,19</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,16</t>
+          <t>-1,27; 0,16</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 1,04</t>
+          <t>-0,77; 1,08</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,01</t>
+          <t>-0,87; 0,92</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,07</t>
+          <t>-1,29; 3,09</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 3,43</t>
+          <t>-0,94; 3,38</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 3,02</t>
+          <t>0,13; 4,19</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,39</t>
+          <t>-0,74; 1,55</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,91</t>
+          <t>-0,41; 1,96</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,71</t>
+          <t>0,04; 2,32</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>56,96%</t>
         </is>
       </c>
     </row>
@@ -2084,42 +2084,42 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-82,45; 489,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-87,66; 373,48</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-28,41; 124,23</t>
+          <t>-28,07; 120,35</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-24,5; 132,67</t>
+          <t>-23,94; 132,43</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-47,94; 113,78</t>
+          <t>-2,25; 162,45</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-36,52; 92,61</t>
+          <t>-28,29; 106,02</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-25,9; 126,24</t>
+          <t>-16,6; 138,6</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-35,21; 109,26</t>
+          <t>-3,11; 150,74</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-3,03</t>
+          <t>-2,85</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-1,28</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-2,36</t>
+          <t>-2,08</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,33; -2,3</t>
+          <t>-5,18; -2,21</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,23; -2,29</t>
+          <t>-5,04; -2,26</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,84; -1,76</t>
+          <t>-4,62; -1,47</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,83</t>
+          <t>-3,26; 0,87</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,23; -0,43</t>
+          <t>-3,95; -0,45</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,48</t>
+          <t>-3,24; 0,58</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,48; -1,13</t>
+          <t>-3,52; -1,04</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,05; -1,66</t>
+          <t>-4,11; -1,71</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,78; -1,17</t>
+          <t>-3,3; -0,9</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-82,86%</t>
+          <t>-77,75%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-26,71%</t>
+          <t>-27,66%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-55,64%</t>
+          <t>-48,93%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -77,46</t>
+          <t>-100,0; -73,95</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -79,75</t>
+          <t>-100,0; -81,23</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-96,38; -63,05</t>
+          <t>-91,0; -52,12</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-56,2; 23,19</t>
+          <t>-55,07; 23,66</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-70,53; -8,63</t>
+          <t>-67,49; -7,19</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-52,13; 14,34</t>
+          <t>-53,93; 16,22</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-71,08; -30,47</t>
+          <t>-69,31; -27,67</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-80,25; -45,63</t>
+          <t>-81,68; -47,57</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-75,78; -34,35</t>
+          <t>-65,41; -26,42</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>0,16</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,23; -0,45</t>
+          <t>-1,25; -0,5</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,12; -0,31</t>
+          <t>-1,11; -0,32</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,28</t>
+          <t>-0,68; 0,27</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,72</t>
+          <t>-1,32; 0,79</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,12</t>
+          <t>-1,73; 0,18</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,97</t>
+          <t>-0,45; 1,39</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,19; -0,05</t>
+          <t>-1,04; -0,05</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,33; -0,24</t>
+          <t>-1,25; -0,25</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,48</t>
+          <t>-0,4; 0,67</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-20,56%</t>
+          <t>-18,92%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-1,21%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-94,18; -46,04</t>
+          <t>-94,18; -45,69</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-84,58; -37,68</t>
+          <t>-84,24; -37,78</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-51,99; 39,75</t>
+          <t>-52,1; 37,53</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-26,05; 19,04</t>
+          <t>-27,57; 20,5</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 3,73</t>
+          <t>-36,49; 5,0</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 25,27</t>
+          <t>-9,18; 38,63</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-39,21; -1,65</t>
+          <t>-35,85; -1,22</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-43,88; -10,37</t>
+          <t>-42,02; -10,49</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-20,17; 20,06</t>
+          <t>-13,4; 29,4</t>
         </is>
       </c>
     </row>
